--- a/AAII_Financials/Yearly/BZZUY_YR_FIN.xlsx
+++ b/AAII_Financials/Yearly/BZZUY_YR_FIN.xlsx
@@ -894,7 +894,7 @@
         <v>10</v>
       </c>
       <c r="D14" s="3">
-        <v>2100</v>
+        <v>10500</v>
       </c>
       <c r="E14" s="3">
         <v>131400</v>
@@ -927,7 +927,7 @@
         <v>11</v>
       </c>
       <c r="D15" s="3">
-        <v>388000</v>
+        <v>379600</v>
       </c>
       <c r="E15" s="3">
         <v>280000</v>
@@ -972,7 +972,7 @@
         <v>12</v>
       </c>
       <c r="D17" s="3">
-        <v>4273200</v>
+        <v>4264800</v>
       </c>
       <c r="E17" s="3">
         <v>3458300</v>
@@ -1005,7 +1005,7 @@
         <v>13</v>
       </c>
       <c r="D18" s="3">
-        <v>1042000</v>
+        <v>1050400</v>
       </c>
       <c r="E18" s="3">
         <v>1019500</v>
